--- a/data/trans_bre/P1413-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1413-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,42</t>
+          <t>4,55</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>117,86%</t>
+          <t>90,54%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 3,42</t>
+          <t>-1,42; 3,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 4,0</t>
+          <t>-1,12; 3,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,94</t>
+          <t>0,67; 4,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 11,6</t>
+          <t>-0,92; 10,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-37,13; 134,76</t>
+          <t>-33,47; 137,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,76; 268,12</t>
+          <t>-35,56; 275,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,83; —</t>
+          <t>13,06; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-21,17; 657,98</t>
+          <t>-17,73; 459,41</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,98</t>
+          <t>4,01</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>56,98%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 5,75</t>
+          <t>-0,43; 5,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 6,44</t>
+          <t>0,41; 6,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 5,21</t>
+          <t>0,58; 5,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 7,42</t>
+          <t>-0,33; 7,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 98,21</t>
+          <t>-6,1; 99,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,78; 182,01</t>
+          <t>6,56; 176,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,05; 289,34</t>
+          <t>9,14; 308,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-22,23; 142,43</t>
+          <t>-6,56; 159,46</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,13</t>
+          <t>10,46</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>100,83%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 3,31</t>
+          <t>-4,15; 3,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,11; 10,49</t>
+          <t>3,5; 10,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 4,87</t>
+          <t>-1,04; 4,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,84; 13,61</t>
+          <t>6,91; 14,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-27,45; 26,09</t>
+          <t>-25,35; 27,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50,72; 214,66</t>
+          <t>41,34; 202,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 94,18</t>
+          <t>-12,44; 87,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>42,16; 153,96</t>
+          <t>53,35; 174,34</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12,2</t>
+          <t>8,3</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>40,87%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 8,85</t>
+          <t>-1,99; 7,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,79; 13,01</t>
+          <t>4,4; 12,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 7,85</t>
+          <t>0,55; 7,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,17; 22,79</t>
+          <t>4,37; 12,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 52,98</t>
+          <t>-9,36; 45,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,25; 181,53</t>
+          <t>40,92; 168,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,59; 99,95</t>
+          <t>4,71; 103,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,23; 327,34</t>
+          <t>19,01; 69,26</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11,87</t>
+          <t>12,79</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>48,37%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 2,47</t>
+          <t>-11,32; 1,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,36; 19,43</t>
+          <t>7,9; 18,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,59; 13,3</t>
+          <t>3,83; 13,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,86; 16,75</t>
+          <t>8,52; 17,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-31,86; 9,91</t>
+          <t>-33,34; 5,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,19; 197,46</t>
+          <t>55,15; 188,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,26; 131,74</t>
+          <t>24,77; 139,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,94; 67,26</t>
+          <t>29,73; 73,75</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36,81</t>
+          <t>19,72</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>136,19%</t>
+          <t>73,08%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,88; 18,17</t>
+          <t>3,07; 17,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,18; 18,7</t>
+          <t>5,8; 19,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,3; 14,16</t>
+          <t>1,71; 13,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,73; 58,07</t>
+          <t>15,21; 25,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,31; 82,76</t>
+          <t>9,37; 77,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,02; 123,52</t>
+          <t>25,12; 130,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,6; 130,37</t>
+          <t>10,19; 122,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>60,2; 247,81</t>
+          <t>51,13; 104,88</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17,51</t>
+          <t>18,01</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>45,26%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 9,85</t>
+          <t>-7,54; 9,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,8; 24,82</t>
+          <t>8,56; 23,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,77; 17,14</t>
+          <t>3,73; 17,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,76; 23,35</t>
+          <t>12,3; 23,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-16,42; 33,89</t>
+          <t>-18,94; 33,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,63; 140,25</t>
+          <t>30,75; 131,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,37; 109,23</t>
+          <t>15,33; 103,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>26,82; 66,68</t>
+          <t>28,29; 64,63</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16,3</t>
+          <t>12,05</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>64,94%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,84</t>
+          <t>1,32; 4,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,52; 10,88</t>
+          <t>7,64; 10,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,42</t>
+          <t>4,21; 7,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,26; 27,92</t>
+          <t>10,2; 13,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,7; 32,62</t>
+          <t>7,52; 31,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>78,62; 132,41</t>
+          <t>78,34; 131,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,84; 97,17</t>
+          <t>48,57; 98,7</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>58,23; 169,73</t>
+          <t>52,31; 80,04</t>
         </is>
       </c>
     </row>
